--- a/artfynd/A 53217-2023 artfynd.xlsx
+++ b/artfynd/A 53217-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53217-2023 artfynd.xlsx
+++ b/artfynd/A 53217-2023 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118043874</v>
+        <v>118043698</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>95384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703701</v>
+        <v>703531</v>
       </c>
       <c r="R4" t="n">
-        <v>7427696</v>
+        <v>7427607</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118043869</v>
+        <v>118038957</v>
       </c>
       <c r="B5" t="n">
-        <v>90941</v>
+        <v>57440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703660</v>
+        <v>703556</v>
       </c>
       <c r="R5" t="n">
-        <v>7427715</v>
+        <v>7427672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118043857</v>
+        <v>118043862</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>90446</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703435</v>
+        <v>703625</v>
       </c>
       <c r="R6" t="n">
-        <v>7427715</v>
+        <v>7427634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118043839</v>
+        <v>118043714</v>
       </c>
       <c r="B7" t="n">
-        <v>90766</v>
+        <v>95384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703435</v>
+        <v>703511</v>
       </c>
       <c r="R7" t="n">
-        <v>7427715</v>
+        <v>7427660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118043638</v>
+        <v>118043722</v>
       </c>
       <c r="B8" t="n">
-        <v>90513</v>
+        <v>97857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703623</v>
+        <v>703490</v>
       </c>
       <c r="R8" t="n">
-        <v>7427507</v>
+        <v>7427641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118043833</v>
+        <v>118043759</v>
       </c>
       <c r="B9" t="n">
-        <v>90425</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,34 +1425,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703442</v>
+        <v>703379</v>
       </c>
       <c r="R9" t="n">
-        <v>7427723</v>
+        <v>7427621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118043862</v>
+        <v>118043839</v>
       </c>
       <c r="B10" t="n">
-        <v>90446</v>
+        <v>90766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1536,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703625</v>
+        <v>703435</v>
       </c>
       <c r="R10" t="n">
-        <v>7427634</v>
+        <v>7427715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118043715</v>
+        <v>118043635</v>
       </c>
       <c r="B11" t="n">
-        <v>90425</v>
+        <v>90446</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703490</v>
+        <v>703623</v>
       </c>
       <c r="R11" t="n">
-        <v>7427641</v>
+        <v>7427507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118043722</v>
+        <v>118043741</v>
       </c>
       <c r="B12" t="n">
-        <v>97857</v>
+        <v>90766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,25 +1740,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>71</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703490</v>
+        <v>703471</v>
       </c>
       <c r="R12" t="n">
-        <v>7427641</v>
+        <v>7427615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118043759</v>
+        <v>118043857</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>79590</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,46 +1842,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703379</v>
+        <v>703435</v>
       </c>
       <c r="R13" t="n">
-        <v>7427621</v>
+        <v>7427715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,11 +1906,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118043706</v>
+        <v>118043869</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>90941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,21 +1948,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703516</v>
+        <v>703660</v>
       </c>
       <c r="R14" t="n">
-        <v>7427644</v>
+        <v>7427715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118043870</v>
+        <v>118043874</v>
       </c>
       <c r="B15" t="n">
-        <v>90890</v>
+        <v>57287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,29 +2050,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703660</v>
+        <v>703701</v>
       </c>
       <c r="R15" t="n">
-        <v>7427715</v>
+        <v>7427696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,6 +2115,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118043741</v>
+        <v>118043706</v>
       </c>
       <c r="B16" t="n">
-        <v>90766</v>
+        <v>97836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,25 +2158,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703471</v>
+        <v>703516</v>
       </c>
       <c r="R16" t="n">
-        <v>7427615</v>
+        <v>7427644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118043698</v>
+        <v>118043715</v>
       </c>
       <c r="B18" t="n">
-        <v>95384</v>
+        <v>90425</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703531</v>
+        <v>703490</v>
       </c>
       <c r="R18" t="n">
-        <v>7427607</v>
+        <v>7427641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118043635</v>
+        <v>118043638</v>
       </c>
       <c r="B19" t="n">
-        <v>90446</v>
+        <v>90513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2463,21 +2468,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2554,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118038957</v>
+        <v>118043870</v>
       </c>
       <c r="B20" t="n">
-        <v>57440</v>
+        <v>90890</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,21 +2570,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703556</v>
+        <v>703660</v>
       </c>
       <c r="R20" t="n">
-        <v>7427672</v>
+        <v>7427715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118043840</v>
+        <v>118043832</v>
       </c>
       <c r="B21" t="n">
-        <v>57398</v>
+        <v>90648</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,47 +2663,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703435</v>
+        <v>703442</v>
       </c>
       <c r="R21" t="n">
-        <v>7427715</v>
+        <v>7427723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118043832</v>
+        <v>118043840</v>
       </c>
       <c r="B22" t="n">
-        <v>90648</v>
+        <v>57398</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,38 +2765,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>703442</v>
+        <v>703435</v>
       </c>
       <c r="R22" t="n">
-        <v>7427723</v>
+        <v>7427715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118043714</v>
+        <v>118043833</v>
       </c>
       <c r="B23" t="n">
-        <v>95384</v>
+        <v>90425</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,21 +2880,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>703511</v>
+        <v>703442</v>
       </c>
       <c r="R23" t="n">
-        <v>7427660</v>
+        <v>7427723</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 53217-2023 artfynd.xlsx
+++ b/artfynd/A 53217-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118043598</v>
+        <v>118043698</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>95386</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703646</v>
+        <v>703531</v>
       </c>
       <c r="R3" t="n">
-        <v>7427528</v>
+        <v>7427607</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118043698</v>
+        <v>118043870</v>
       </c>
       <c r="B4" t="n">
-        <v>95384</v>
+        <v>90892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703531</v>
+        <v>703660</v>
       </c>
       <c r="R4" t="n">
-        <v>7427607</v>
+        <v>7427715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118038957</v>
+        <v>118043869</v>
       </c>
       <c r="B5" t="n">
-        <v>57440</v>
+        <v>90943</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703556</v>
+        <v>703660</v>
       </c>
       <c r="R5" t="n">
-        <v>7427672</v>
+        <v>7427715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118043862</v>
+        <v>118043857</v>
       </c>
       <c r="B6" t="n">
-        <v>90446</v>
+        <v>79592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703625</v>
+        <v>703435</v>
       </c>
       <c r="R6" t="n">
-        <v>7427634</v>
+        <v>7427715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118043714</v>
+        <v>118043715</v>
       </c>
       <c r="B7" t="n">
-        <v>95384</v>
+        <v>90427</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703511</v>
+        <v>703490</v>
       </c>
       <c r="R7" t="n">
-        <v>7427660</v>
+        <v>7427641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118043722</v>
+        <v>118043832</v>
       </c>
       <c r="B8" t="n">
-        <v>97857</v>
+        <v>90650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703490</v>
+        <v>703442</v>
       </c>
       <c r="R8" t="n">
-        <v>7427641</v>
+        <v>7427723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1397,7 @@
         <v>118043759</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118043839</v>
+        <v>118043714</v>
       </c>
       <c r="B10" t="n">
-        <v>90766</v>
+        <v>95386</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,25 +1521,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703435</v>
+        <v>703511</v>
       </c>
       <c r="R10" t="n">
-        <v>7427715</v>
+        <v>7427660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118043635</v>
+        <v>118043719</v>
       </c>
       <c r="B11" t="n">
-        <v>90446</v>
+        <v>79592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703623</v>
+        <v>703490</v>
       </c>
       <c r="R11" t="n">
-        <v>7427507</v>
+        <v>7427641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1716,7 @@
         <v>118043741</v>
       </c>
       <c r="B12" t="n">
-        <v>90766</v>
+        <v>90768</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118043857</v>
+        <v>118043598</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,38 +1827,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703435</v>
+        <v>703646</v>
       </c>
       <c r="R13" t="n">
-        <v>7427715</v>
+        <v>7427528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,6 +1896,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118043869</v>
+        <v>118043638</v>
       </c>
       <c r="B14" t="n">
-        <v>90941</v>
+        <v>90515</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703660</v>
+        <v>703623</v>
       </c>
       <c r="R14" t="n">
-        <v>7427715</v>
+        <v>7427507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118043874</v>
+        <v>118043833</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>90427</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,39 +2045,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703701</v>
+        <v>703442</v>
       </c>
       <c r="R15" t="n">
-        <v>7427696</v>
+        <v>7427723</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,11 +2105,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118043706</v>
+        <v>118043840</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,38 +2143,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703516</v>
+        <v>703435</v>
       </c>
       <c r="R16" t="n">
-        <v>7427644</v>
+        <v>7427715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,10 +2242,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118043719</v>
+        <v>118043706</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,25 +2254,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2288,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703490</v>
+        <v>703516</v>
       </c>
       <c r="R17" t="n">
-        <v>7427641</v>
+        <v>7427644</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2344,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118043715</v>
+        <v>118043862</v>
       </c>
       <c r="B18" t="n">
-        <v>90425</v>
+        <v>90448</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,21 +2360,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2384,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703490</v>
+        <v>703625</v>
       </c>
       <c r="R18" t="n">
-        <v>7427641</v>
+        <v>7427634</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118043638</v>
+        <v>118043635</v>
       </c>
       <c r="B19" t="n">
-        <v>90513</v>
+        <v>90448</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,21 +2462,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2548,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118043870</v>
+        <v>118043874</v>
       </c>
       <c r="B20" t="n">
-        <v>90890</v>
+        <v>57288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,29 +2564,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703660</v>
+        <v>703701</v>
       </c>
       <c r="R20" t="n">
-        <v>7427715</v>
+        <v>7427696</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,6 +2629,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2651,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118043832</v>
+        <v>118038957</v>
       </c>
       <c r="B21" t="n">
-        <v>90648</v>
+        <v>57441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,25 +2672,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2691,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703442</v>
+        <v>703556</v>
       </c>
       <c r="R21" t="n">
-        <v>7427723</v>
+        <v>7427672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118043840</v>
+        <v>118043722</v>
       </c>
       <c r="B22" t="n">
-        <v>57398</v>
+        <v>97859</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2769,43 +2778,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>703435</v>
+        <v>703490</v>
       </c>
       <c r="R22" t="n">
-        <v>7427715</v>
+        <v>7427641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118043833</v>
+        <v>118043839</v>
       </c>
       <c r="B23" t="n">
-        <v>90425</v>
+        <v>90768</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2876,25 +2876,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3242</v>
+        <v>71</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>703442</v>
+        <v>703435</v>
       </c>
       <c r="R23" t="n">
-        <v>7427723</v>
+        <v>7427715</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 53217-2023 artfynd.xlsx
+++ b/artfynd/A 53217-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91820518</v>
+        <v>118043698</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åkåskielas-Halmape, Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703677.0290876587</v>
+        <v>703531</v>
       </c>
       <c r="R2" t="n">
-        <v>7427702.081613109</v>
+        <v>7427607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118043635</v>
+        <v>118043714</v>
       </c>
       <c r="B3" t="n">
-        <v>90451</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703623</v>
+        <v>703511</v>
       </c>
       <c r="R3" t="n">
-        <v>7427507</v>
+        <v>7427660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118043698</v>
+        <v>118043741</v>
       </c>
       <c r="B4" t="n">
-        <v>95394</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703531</v>
+        <v>703471</v>
       </c>
       <c r="R4" t="n">
-        <v>7427607</v>
+        <v>7427615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118043722</v>
+        <v>118043839</v>
       </c>
       <c r="B5" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>71</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703490</v>
+        <v>703435</v>
       </c>
       <c r="R5" t="n">
-        <v>7427641</v>
+        <v>7427715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118043741</v>
+        <v>118043635</v>
       </c>
       <c r="B6" t="n">
-        <v>90772</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703471</v>
+        <v>703623</v>
       </c>
       <c r="R6" t="n">
-        <v>7427615</v>
+        <v>7427507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118038957</v>
+        <v>118043862</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703556</v>
+        <v>703625</v>
       </c>
       <c r="R7" t="n">
-        <v>7427672</v>
+        <v>7427634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118043833</v>
+        <v>118039593</v>
       </c>
       <c r="B8" t="n">
-        <v>90430</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>385</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703442</v>
+        <v>703603</v>
       </c>
       <c r="R8" t="n">
-        <v>7427723</v>
+        <v>7427691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,58 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118043759</v>
+        <v>91820519</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Åkåskielas-Halmape, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703379</v>
+        <v>703588</v>
       </c>
       <c r="R9" t="n">
-        <v>7427621</v>
+        <v>7427481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Håkan Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118043598</v>
+        <v>91820518</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,39 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Åkåskielas-Halmape, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703646</v>
+        <v>703677</v>
       </c>
       <c r="R10" t="n">
-        <v>7427528</v>
+        <v>7427702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,57 +1536,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Håkan Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118043870</v>
+        <v>118043638</v>
       </c>
       <c r="B11" t="n">
-        <v>90896</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>1204</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703660</v>
+        <v>703623</v>
       </c>
       <c r="R11" t="n">
-        <v>7427715</v>
+        <v>7427507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,56 +1645,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118043840</v>
+        <v>118043869</v>
       </c>
       <c r="B12" t="n">
-        <v>57401</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703435</v>
+        <v>703660</v>
       </c>
       <c r="R12" t="n">
         <v>7427715</v>
@@ -1834,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118043706</v>
+        <v>118043832</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703516</v>
+        <v>703442</v>
       </c>
       <c r="R13" t="n">
-        <v>7427644</v>
+        <v>7427723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,53 +1839,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118043869</v>
+        <v>90907586</v>
       </c>
       <c r="B14" t="n">
-        <v>90947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703660</v>
+        <v>703316</v>
       </c>
       <c r="R14" t="n">
-        <v>7427715</v>
+        <v>7427714</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,31 +1920,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118043862</v>
+        <v>118043807</v>
       </c>
       <c r="B15" t="n">
-        <v>90451</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,34 +1956,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703625</v>
+        <v>703322</v>
       </c>
       <c r="R15" t="n">
-        <v>7427634</v>
+        <v>7427711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,15 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118043874</v>
+        <v>118043715</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,39 +2053,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703701</v>
+        <v>703490</v>
       </c>
       <c r="R16" t="n">
-        <v>7427696</v>
+        <v>7427641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,11 +2113,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,50 +2139,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118043839</v>
+        <v>118043833</v>
       </c>
       <c r="B17" t="n">
-        <v>90772</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703435</v>
+        <v>703442</v>
       </c>
       <c r="R17" t="n">
-        <v>7427715</v>
+        <v>7427723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,50 +2236,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118043714</v>
+        <v>118043809</v>
       </c>
       <c r="B18" t="n">
-        <v>95394</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703511</v>
+        <v>703322</v>
       </c>
       <c r="R18" t="n">
-        <v>7427660</v>
+        <v>7427711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,15 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118043715</v>
+        <v>118043805</v>
       </c>
       <c r="B19" t="n">
-        <v>90430</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2472,34 +2344,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703490</v>
+        <v>703322</v>
       </c>
       <c r="R19" t="n">
-        <v>7427641</v>
+        <v>7427711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,50 +2430,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118043638</v>
+        <v>118043719</v>
       </c>
       <c r="B20" t="n">
-        <v>90518</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703623</v>
+        <v>703490</v>
       </c>
       <c r="R20" t="n">
-        <v>7427507</v>
+        <v>7427641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,15 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118043719</v>
+        <v>118043857</v>
       </c>
       <c r="B21" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,14 +2558,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703490</v>
+        <v>703435</v>
       </c>
       <c r="R21" t="n">
-        <v>7427641</v>
+        <v>7427715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,50 +2624,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118043832</v>
+        <v>118038087</v>
       </c>
       <c r="B22" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>703442</v>
+        <v>703557</v>
       </c>
       <c r="R22" t="n">
-        <v>7427723</v>
+        <v>7427761</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,6 +2700,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,50 +2731,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118043857</v>
+        <v>118043598</v>
       </c>
       <c r="B23" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ågåsgielas (Ågåsgielas), Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>703435</v>
+        <v>703646</v>
       </c>
       <c r="R23" t="n">
-        <v>7427715</v>
+        <v>7427528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,6 +2809,11 @@
           <t>2024-06-27</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2963,6 +2835,814 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118043759</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>703379</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7427621</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118043874</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>703701</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7427696</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118038957</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>703556</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7427672</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118043840</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>703435</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7427715</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118043706</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>703516</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7427644</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118043722</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>703490</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7427641</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118043647</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>703619</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7427481</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118043870</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>703660</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7427715</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53217-2023 artfynd.xlsx
+++ b/artfynd/A 53217-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043741</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043839</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043635</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118039593</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820519</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820518</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043869</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907586</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043807</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043833</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043809</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043805</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043719</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043857</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2728,6 +2833,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118038087</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2835,6 +2945,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043598</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,6 +3060,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043759</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3052,6 +3172,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043874</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118038957</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3255,6 +3385,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043840</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3352,6 +3487,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043706</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3449,6 +3589,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043722</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3546,6 +3691,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043647</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3643,8 +3793,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118043870</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>